--- a/16_Crypto_Digital_Assets/_template_CRYPTO.xlsx
+++ b/16_Crypto_Digital_Assets/_template_CRYPTO.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Valuation" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Staking Yield" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Comparable Protocols" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="RefreshLog" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Supply Emission Schedule" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="RefreshLog" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="76">
   <si>
     <t xml:space="preserve">[TOKEN] — Crypto / Digital Asset Model</t>
   </si>
@@ -180,9 +181,15 @@
     <t xml:space="preserve">Mkt cap</t>
   </si>
   <si>
+    <t xml:space="preserve">FDV</t>
+  </si>
+  <si>
     <t xml:space="preserve">TVL</t>
   </si>
   <si>
+    <t xml:space="preserve">Daily volume</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mkt/TVL</t>
   </si>
   <si>
@@ -190,6 +197,45 @@
   </si>
   <si>
     <t xml:space="preserve">NVT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This protocol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forward Supply Emission &amp; Dilution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual emission rate (% of max supply issued/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simplified: assumes a flat schedule. Real unlocks are usually cliff + linear per allocation — treat this as a planning approximation, not a substitute for the actual unlock table.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Circulating supply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative dilution vs. today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implied mkt cap at today's price (if price held flat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A holder who doesn't add to their position loses this much ownership share to new issuance over time -- the price needs to grow faster than dilution just to keep the position's dollar value from falling.</t>
   </si>
   <si>
     <t xml:space="preserve">Refresh Log</t>
@@ -222,7 +268,7 @@
     <numFmt numFmtId="168" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="169" formatCode="0.0\x"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,6 +335,13 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -365,108 +418,116 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -723,56 +784,56 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C8"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
     </row>
@@ -793,149 +854,149 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:F13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="8" t="str">
+      <c r="C5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="str">
         <f aca="false">IFERROR(C5/$C$10,"-")</f>
         <v>-</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="8" t="str">
+      <c r="C6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="str">
         <f aca="false">IFERROR(C6/$C$10,"-")</f>
         <v>-</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="8" t="str">
+      <c r="C7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9" t="str">
         <f aca="false">IFERROR(C7/$C$10,"-")</f>
         <v>-</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="8" t="str">
+      <c r="C8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9" t="str">
         <f aca="false">IFERROR(C8/$C$10,"-")</f>
         <v>-</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="8" t="str">
+      <c r="C9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9" t="str">
         <f aca="false">IFERROR(C9/$C$10,"-")</f>
         <v>-</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="10" t="n">
+      <c r="C10" s="11" t="n">
         <f aca="false">SUM(C5:C9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="8" t="str">
+      <c r="C13" s="9" t="str">
         <f aca="false">IFERROR(C12/C10,"-")</f>
         <v>-</v>
       </c>
@@ -957,115 +1018,115 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="13" t="n">
+      <c r="C5" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <f aca="false">C5*Tokenomics!C12</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <f aca="false">C5*Tokenomics!C10</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="16" t="str">
+      <c r="C13" s="17" t="str">
         <f aca="false">IFERROR(C11/C6,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="16" t="str">
+      <c r="C14" s="17" t="str">
         <f aca="false">IFERROR(C12/C6,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C15" s="16" t="str">
+      <c r="C15" s="17" t="str">
         <f aca="false">IFERROR(C11/C7,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="16" t="str">
+      <c r="C16" s="17" t="str">
         <f aca="false">IFERROR(C11/(C8*365),"-")</f>
         <v>-</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="10" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1086,97 +1147,97 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:D14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="20" t="n">
         <f aca="false">C5*Tokenomics!C12</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="20" t="str">
+      <c r="C12" s="21" t="str">
         <f aca="false">IFERROR(C6/C11,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="20" t="str">
+      <c r="C13" s="21" t="str">
         <f aca="false">IFERROR(C7/(C11*C8),"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="21" t="str">
+      <c r="C14" s="22" t="str">
         <f aca="false">IFERROR(C13-C12,"-")</f>
         <v>-</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="10" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1196,179 +1257,252 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A2:G11"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A2:I11"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>54</v>
       </c>
+      <c r="H4" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="23" t="n">
+        <f aca="false">Valuation!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <f aca="false">Valuation!C12</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <f aca="false">Valuation!C6</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="23" t="n">
+        <f aca="false">Valuation!C8</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="17" t="str">
+        <f aca="false">IFERROR(C5/E5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H5" s="17" t="str">
+        <f aca="false">IFERROR(D5/E5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I5" s="17" t="str">
+        <f aca="false">IFERROR(C5/(F5*365),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="22" t="s">
+      <c r="C6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="17" t="str">
+        <f aca="false">IFERROR(C6/E6,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H6" s="17" t="str">
+        <f aca="false">IFERROR(D6/E6,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I6" s="17" t="str">
+        <f aca="false">IFERROR(C6/(F6*365),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="22" t="s">
+      <c r="C7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="17" t="str">
+        <f aca="false">IFERROR(C7/E7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H7" s="17" t="str">
+        <f aca="false">IFERROR(D7/E7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I7" s="17" t="str">
+        <f aca="false">IFERROR(C7/(F7*365),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="22" t="s">
+      <c r="C8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="17" t="str">
+        <f aca="false">IFERROR(C8/E8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H8" s="17" t="str">
+        <f aca="false">IFERROR(D8/E8,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I8" s="17" t="str">
+        <f aca="false">IFERROR(C8/(F8*365),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="22" t="s">
+      <c r="C9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="17" t="str">
+        <f aca="false">IFERROR(C9/E9,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H9" s="17" t="str">
+        <f aca="false">IFERROR(D9/E9,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I9" s="17" t="str">
+        <f aca="false">IFERROR(C9/(F9*365),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="22" t="s">
+      <c r="C10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="17" t="str">
+        <f aca="false">IFERROR(C10/E10,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H10" s="17" t="str">
+        <f aca="false">IFERROR(D10/E10,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I10" s="17" t="str">
+        <f aca="false">IFERROR(C10/(F10*365),"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="C11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>0</v>
+      <c r="C11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="17" t="str">
+        <f aca="false">IFERROR(C11/E11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H11" s="17" t="str">
+        <f aca="false">IFERROR(D11/E11,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="I11" s="17" t="str">
+        <f aca="false">IFERROR(C11/(F11*365),"-")</f>
+        <v>-</v>
       </c>
     </row>
   </sheetData>
@@ -1387,107 +1521,245 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:G10"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="40"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>55</v>
+      <c r="B2" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="B4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="C4" s="18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D4" s="10" t="s">
         <v>60</v>
       </c>
     </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C6" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="26" t="n">
+        <f aca="false">Tokenomics!C12</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="20" t="n">
+        <f aca="false">MIN(Tokenomics!$C$10,C7+Tokenomics!$C$10*$C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <f aca="false">MIN(Tokenomics!$C$10,D7+Tokenomics!$C$10*$C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="20" t="n">
+        <f aca="false">MIN(Tokenomics!$C$10,E7+Tokenomics!$C$10*$C$4)</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="20" t="n">
+        <f aca="false">MIN(Tokenomics!$C$10,F7+Tokenomics!$C$10*$C$4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="21" t="str">
+        <f aca="false">IFERROR(1-$C$7/C7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D8" s="21" t="str">
+        <f aca="false">IFERROR(1-$C$7/D7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E8" s="21" t="str">
+        <f aca="false">IFERROR(1-$C$7/E7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F8" s="21" t="str">
+        <f aca="false">IFERROR(1-$C$7/F7,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G8" s="21" t="str">
+        <f aca="false">IFERROR(1-$C$7/G7,"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <f aca="false">Valuation!$C$5*C7</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">Valuation!$C$5*D7</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <f aca="false">Valuation!$C$5*E7</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <f aca="false">Valuation!$C$5*F7</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <f aca="false">Valuation!$C$5*G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="10" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:F14"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+      <c r="F5" s="27"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="27"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="27"/>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/16_Crypto_Digital_Assets/_template_CRYPTO.xlsx
+++ b/16_Crypto_Digital_Assets/_template_CRYPTO.xlsx
@@ -868,11 +868,11 @@
         </is>
       </c>
       <c r="C13" s="25">
-        <f>IFERROR(Valuation!C12/Valuation!C11,0)</f>
+        <f>IFERROR(Valuation!C12/Valuation!C11,"-")</f>
         <v/>
       </c>
       <c r="D13" s="25">
-        <f>IF(C13&lt;=2,"PASS",IF(C13&lt;=5,"REVIEW","BREACH"))</f>
+        <f>IF(ISNUMBER(C13),IF(C13&lt;=2,"PASS",IF(C13&lt;=5,"REVIEW","BREACH")),"REVIEW")</f>
         <v/>
       </c>
       <c r="E13" t="inlineStr">
